--- a/data/trans_orig/P21D_4_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216624</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>441364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,62 +1108,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3503</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178960</t>
+          <t>178110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176766</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356196</t>
+          <t>356838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,62 +1451,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414192</t>
+          <t>414191</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>409958</t>
+          <t>407990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77787</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488123</t>
+          <t>488181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>449593</t>
+          <t>449420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330588</t>
+          <t>330505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337204</t>
+          <t>337213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>783111</t>
+          <t>784273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>791983</t>
+          <t>792380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,82 +2117,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10195</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>9895</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4941</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9853</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>4941</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,82 +2230,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>410915</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>405661</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>414106</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>633015</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>628061</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>635688</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>410915</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>406003</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>414011</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>633015</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>628193</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>635728</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312944</t>
+          <t>312962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436144</t>
+          <t>436333</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>440880</t>
+          <t>440862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1613950</t>
+          <t>1614921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1622360</t>
+          <t>1622396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1530975</t>
+          <t>1531205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1541541</t>
+          <t>1541354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3149602</t>
+          <t>3148702</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3162411</t>
+          <t>3161992</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_4_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Clase-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>181094</t>
+          <t>196341</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178110</t>
+          <t>193779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>359129</t>
+          <t>392963</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356838</t>
+          <t>390559</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>414191</t>
+          <t>187842</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407990</t>
+          <t>183854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>493143</t>
+          <t>274463</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>488181</t>
+          <t>270473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>454203</t>
+          <t>510031</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>449420</t>
+          <t>505824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>334919</t>
+          <t>382085</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330505</t>
+          <t>378013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337213</t>
+          <t>384850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>789121</t>
+          <t>892116</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>784273</t>
+          <t>886450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>792380</t>
+          <t>895816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>794765</t>
+          <t>898501</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>794765</t>
+          <t>898501</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>794765</t>
+          <t>898501</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>410915</t>
+          <t>382639</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>405661</t>
+          <t>378117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>414106</t>
+          <t>385436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>633015</t>
+          <t>648646</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>628061</t>
+          <t>644203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>635688</t>
+          <t>651411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>637956</t>
+          <t>653888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,22 +2510,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>316145</t>
+          <t>352408</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312962</t>
+          <t>349402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317542</t>
+          <t>353970</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>439473</t>
+          <t>469845</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>436333</t>
+          <t>467022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>440862</t>
+          <t>471322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>318122</t>
+          <t>354500</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>441450</t>
+          <t>471937</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1619853</t>
+          <t>1522069</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1614921</t>
+          <t>1516929</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1622396</t>
+          <t>1524464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1536919</t>
+          <t>1635198</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1531205</t>
+          <t>1628437</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1541354</t>
+          <t>1640015</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3156772</t>
+          <t>3157267</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3148702</t>
+          <t>3150053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3161992</t>
+          <t>3162591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1547675</t>
+          <t>1647114</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3170909</t>
+          <t>3172567</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3170909</t>
+          <t>3172567</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3170909</t>
+          <t>3172567</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
